--- a/AAII_Financials/Yearly/BAOS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BAOS_YR_FIN.xlsx
@@ -958,7 +958,7 @@
         <v>-500</v>
       </c>
       <c r="F14" s="3">
-        <v>-500</v>
+        <v>-600</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>500</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>-300</v>
@@ -1201,7 +1201,7 @@
         <v>-26900</v>
       </c>
       <c r="F21" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="G21" s="3">
         <v>-23400</v>
@@ -1663,7 +1663,7 @@
         <v>-500</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
         <v>300</v>
@@ -3497,7 +3497,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
